--- a/data/zh-cn/age.xlsx
+++ b/data/zh-cn/age.xlsx
@@ -1259,7 +1259,7 @@
         <v/>
       </c>
       <c r="AK7" t="str">
-        <v/>
+        <v>30143</v>
       </c>
       <c r="AL7" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v/>
       </c>
       <c r="AK9" t="str">
-        <v/>
+        <v>30144</v>
       </c>
       <c r="AL9" t="str">
         <v/>
@@ -2134,7 +2134,7 @@
         <v/>
       </c>
       <c r="AK14" t="str">
-        <v/>
+        <v>30145</v>
       </c>
       <c r="AL14" t="str">
         <v/>
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="AK20" t="str">
-        <v/>
+        <v>30146</v>
       </c>
       <c r="AL20" t="str">
         <v/>
@@ -3634,7 +3634,7 @@
         <v/>
       </c>
       <c r="AK26" t="str">
-        <v/>
+        <v>30147</v>
       </c>
       <c r="AL26" t="str">
         <v/>
@@ -4384,7 +4384,7 @@
         <v/>
       </c>
       <c r="AK32" t="str">
-        <v/>
+        <v>30148</v>
       </c>
       <c r="AL32" t="str">
         <v/>
@@ -4759,7 +4759,7 @@
         <v/>
       </c>
       <c r="AK35" t="str">
-        <v/>
+        <v>30149</v>
       </c>
       <c r="AL35" t="str">
         <v/>
@@ -5134,7 +5134,7 @@
         <v/>
       </c>
       <c r="AK38" t="str">
-        <v/>
+        <v>30150</v>
       </c>
       <c r="AL38" t="str">
         <v/>
@@ -5634,7 +5634,7 @@
         <v/>
       </c>
       <c r="AK42" t="str">
-        <v/>
+        <v>30151</v>
       </c>
       <c r="AL42" t="str">
         <v/>
@@ -6634,7 +6634,7 @@
         <v/>
       </c>
       <c r="AK50" t="str">
-        <v/>
+        <v>30152</v>
       </c>
       <c r="AL50" t="str">
         <v/>
@@ -7384,7 +7384,7 @@
         <v/>
       </c>
       <c r="AK56" t="str">
-        <v/>
+        <v>30153</v>
       </c>
       <c r="AL56" t="str">
         <v/>
@@ -7884,7 +7884,7 @@
         <v/>
       </c>
       <c r="AK60" t="str">
-        <v/>
+        <v>30154</v>
       </c>
       <c r="AL60" t="str">
         <v/>
@@ -8384,7 +8384,7 @@
         <v/>
       </c>
       <c r="AK64" t="str">
-        <v/>
+        <v>30155</v>
       </c>
       <c r="AL64" t="str">
         <v/>
@@ -10384,7 +10384,7 @@
         <v/>
       </c>
       <c r="AK80" t="str">
-        <v/>
+        <v>30156</v>
       </c>
       <c r="AL80" t="str">
         <v/>
@@ -10884,7 +10884,7 @@
         <v/>
       </c>
       <c r="AK84" t="str">
-        <v/>
+        <v>30157</v>
       </c>
       <c r="AL84" t="str">
         <v/>
@@ -11634,7 +11634,7 @@
         <v/>
       </c>
       <c r="AK90" t="str">
-        <v/>
+        <v>30158</v>
       </c>
       <c r="AL90" t="str">
         <v/>
